--- a/output/pdf_financials_xlsx/PPX.xlsx
+++ b/output/pdf_financials_xlsx/PPX.xlsx
@@ -1309,22 +1309,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7.224209</v>
+        <v>-7.224209</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8.089917</v>
+        <v>-8.089917</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>9.668455</v>
+        <v>-9.668455</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.400812</v>
+        <v>-0.400812</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.087274</v>
+        <v>-2.087274</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>25.230703</v>
+        <v>-25.230703</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-5.337489</v>
@@ -1627,22 +1627,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.224209</v>
+        <v>-7.224209</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>8.089917</v>
+        <v>-8.089917</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9.668455</v>
+        <v>-9.668455</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.400812</v>
+        <v>-0.400812</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.087274</v>
+        <v>-2.087274</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>25.230703</v>
+        <v>-25.230703</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-5.337489</v>
@@ -1812,22 +1812,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7.224209</v>
+        <v>-7.224209</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8.089917</v>
+        <v>-8.089917</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>9.668455</v>
+        <v>-9.668455</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.400812</v>
+        <v>-0.400812</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.087274</v>
+        <v>-2.087274</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.230703</v>
+        <v>-25.230703</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-5.337489</v>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>240.806967</v>
+        <v>-240.806967</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>483.42275</v>
+        <v>-483.42275</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-104.3637</v>
+        <v>104.3637</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-114.685014</v>
+        <v>114.685014</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>133.437225</v>
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.224209</v>
+        <v>-7.224209</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.089917</v>
+        <v>-8.089917</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.668455</v>
+        <v>-9.668455</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.439317</v>
+        <v>-0.362307</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.116142</v>
+        <v>-2.058406</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>25.230703</v>
+        <v>-25.230703</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.337489</v>
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.276645</v>
+        <v>-7.171773</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.145844</v>
+        <v>-8.033989999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.727596</v>
+        <v>-9.609313999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.442582</v>
+        <v>-0.359042</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.126403</v>
+        <v>-2.048145</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>25.242176</v>
+        <v>-25.21923</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.323763</v>
@@ -2374,22 +2374,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -6167,46 +6167,46 @@
         <v>3.459985</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>4.027601</v>
+        <v>4.502309</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.723412</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.008139</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>8.251322999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.643166</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.9053</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.130882</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.288579</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.349642</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.951343</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.466854</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.868113</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>8.866754999999999</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>8.790524</v>
       </c>
     </row>
     <row r="93">
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>7.224209</v>
+        <v>-7.224209</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>8.089917</v>
+        <v>-8.089917</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>9.668455</v>
+        <v>-9.668455</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.400812</v>
@@ -10864,7 +10864,11 @@
           <t>Reserves (note 15)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -15154,7 +15158,11 @@
           <t>Reserves (note 15)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15998,7 +16006,11 @@
           <t>Reserves (note 14)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -17066,7 +17078,11 @@
           <t>Reserves (note 14)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -19018,7 +19034,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -19868,7 +19888,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -20506,7 +20530,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21574,7 +21602,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -23786,7 +23818,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -23890,7 +23926,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -25060,7 +25100,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -25162,7 +25206,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -27514,7 +27562,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -27618,7 +27670,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -89010,7 +89066,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpense</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -93234,13 +93290,13 @@
         </is>
       </c>
       <c r="I804" s="5" t="n">
-        <v>2.087274</v>
+        <v>-2.087274</v>
       </c>
       <c r="J804" s="5" t="n">
-        <v>25.230703</v>
+        <v>-25.230703</v>
       </c>
       <c r="K804" s="5" t="n">
-        <v>5.337489</v>
+        <v>-5.337489</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -95449,10 +95505,10 @@
         </is>
       </c>
       <c r="H825" s="5" t="n">
-        <v>0.400812</v>
+        <v>-0.400812</v>
       </c>
       <c r="I825" s="5" t="n">
-        <v>2.049099</v>
+        <v>-2.049099</v>
       </c>
       <c r="J825" t="inlineStr">
         <is>
@@ -97136,10 +97192,10 @@
         </is>
       </c>
       <c r="G841" s="5" t="n">
-        <v>9.668455</v>
+        <v>-9.668455</v>
       </c>
       <c r="H841" s="5" t="n">
-        <v>0.865708</v>
+        <v>-0.865708</v>
       </c>
       <c r="I841" t="inlineStr">
         <is>
@@ -98815,10 +98871,10 @@
         </is>
       </c>
       <c r="F857" s="5" t="n">
-        <v>8.089917</v>
+        <v>-8.089917</v>
       </c>
       <c r="G857" s="5" t="n">
-        <v>0.651823</v>
+        <v>-0.651823</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
@@ -100712,10 +100768,10 @@
         </is>
       </c>
       <c r="E875" s="5" t="n">
-        <v>7.224209</v>
+        <v>-7.224209</v>
       </c>
       <c r="F875" s="5" t="n">
-        <v>1.361697</v>
+        <v>-1.361697</v>
       </c>
       <c r="G875" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PPX.xlsx
+++ b/output/pdf_financials_xlsx/PPX.xlsx
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.109273</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.029123</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1077,13 +1077,13 @@
         <v>-0.038505</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.028868</v>
+        <v>-0.007944</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014835</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057006</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1107,16 +1107,16 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>5.852396</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>8.689598</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.518182</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>9.315405</v>
       </c>
     </row>
     <row r="13">
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.224209</v>
+        <v>-7.114936</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.089917</v>
+        <v>-8.060794</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-9.668455</v>
@@ -2102,13 +2102,13 @@
         <v>-0.362307</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.058406</v>
+        <v>-2.07933</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-25.230703</v>
+        <v>-25.215868</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.337489</v>
+        <v>-5.280483</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.422382</v>
@@ -2132,13 +2132,13 @@
         <v>-2.3852</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.299484</v>
+        <v>-5.552912</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.188129</v>
+        <v>-5.501469</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-5.745332</v>
+        <v>-6.263514</v>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.171773</v>
+        <v>-7.0625</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.033989999999999</v>
+        <v>-8.004867000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-9.609313999999999</v>
@@ -2226,13 +2226,13 @@
         <v>-0.359042</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.048145</v>
+        <v>-2.069069</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-25.21923</v>
+        <v>-25.204395</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.323763</v>
+        <v>-5.266757</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.412468</v>
@@ -2256,13 +2256,13 @@
         <v>-2.38481</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.299681</v>
+        <v>-5.552715</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.194291</v>
+        <v>-5.495307</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.739535</v>
+        <v>-6.257717</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2553,46 +2553,46 @@
         <v>6.563203</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.034556</v>
+        <v>0.033958</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.185569</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.056795</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.218804</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.50914</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.536341</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.45543</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.084262</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.028676</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.336242</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.345207</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.803751</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>3.032136</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>5.157014</v>
       </c>
     </row>
     <row r="35">
@@ -2675,46 +2675,46 @@
         <v>6.563203</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.034556</v>
+        <v>0.033958</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.185569</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.056795</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.218804</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.50914</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.536341</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.45543</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.084262</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.028676</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.336242</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.345207</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.803751</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>3.032136</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>5.157014</v>
       </c>
     </row>
     <row r="37">
@@ -3407,46 +3407,46 @@
         <v>0.25011</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005741</v>
+        <v>0.006339</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.081599</v>
+        <v>0.024804</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.239395</v>
+        <v>0.020591</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.558666</v>
+        <v>0.049526</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.64442</v>
+        <v>0.108079</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.520558</v>
+        <v>0.06512800000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.109097</v>
+        <v>0.024835</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.029327</v>
+        <v>0.000651</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.336832</v>
+        <v>0.00059</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.096034</v>
+        <v>0.750827</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.833689</v>
+        <v>0.029938</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.047912</v>
+        <v>0.015776</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>5.184036</v>
+        <v>0.027022</v>
       </c>
     </row>
     <row r="49">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -21928,7 +21928,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -80012,7 +80012,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -81728,7 +81728,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -89066,7 +89066,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -90314,7 +90314,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -91472,7 +91472,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -91578,7 +91578,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -92840,7 +92840,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -94004,7 +94004,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -100552,7 +100552,7 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E873" s="5" t="n">

--- a/output/pdf_financials_xlsx/PPX.xlsx
+++ b/output/pdf_financials_xlsx/PPX.xlsx
@@ -1420,7 +1420,7 @@
         <v>2.94027</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.418298</v>
+        <v>-0.418298</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>-0</v>
@@ -4439,22 +4439,22 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.638648</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.546311</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.86896</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.827221</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>2.727659</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>2.721229</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>0.112632</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>7.1e-05</v>
       </c>
       <c r="N107" s="3" t="n">
         <v>0</v>
@@ -7213,31 +7213,31 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.011108</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.013884</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.01666</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.002814</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.002792</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.001411</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.510039</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.182393</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -7255,16 +7255,16 @@
         <v>0</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.049668</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.295311</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.431178</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.396474</v>
       </c>
     </row>
     <row r="111">
@@ -31542,7 +31542,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -40668,7 +40672,11 @@
           <t>Finders' shares issued with private placement $</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -42206,7 +42214,11 @@
           <t>Proceeds from private placement 14</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -44316,7 +44328,11 @@
           <t>Share based payments expense</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -54120,7 +54136,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -71506,7 +71526,11 @@
           <t>Accretion expense 2,776</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E596" s="5" t="n">
         <v>0.011108</v>
       </c>
@@ -82044,7 +82068,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E697" t="inlineStr">
         <is>
           <t>-</t>
